--- a/20260816_TSV_Template_V1.00.xlsx
+++ b/20260816_TSV_Template_V1.00.xlsx
@@ -304,19 +304,6 @@
 空だとテーマ別弱点分析と弱点ノックの対象外になります。</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>【任意】
-split と書くと、「本日の復習」で1肢だけの一問一答（○×）として
-出ることがあります。空欄なら今までどおり4択のままです。
-この列そのものが無くても取り込めます。
-★書かないほうが安全な問題★
-・「最も近いのはどれか」など、選択肢どうしを比べないと
-  答えが決まらない問題（1肢に切り出すと成立しません）
-・「誤っているのはどれか」など、正誤の向きが反転している問題
-迷ったら空欄のままで大丈夫です（4択で出るだけ）。</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -845,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -860,7 +847,6 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -924,11 +910,6 @@
           <t>タグ（推奨）</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
-        <is>
-          <t>分割（任意）</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -991,11 +972,6 @@
           <t>[["#人口動態統計"],["#人口動態統計"],["#人口動態統計"],["#人口動態統計"]]</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1054,7 +1030,6 @@
           <t>[["#保健師助産師看護師法"]]</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n"/>
@@ -1069,7 +1044,6 @@
       <c r="J4" s="7" t="n"/>
       <c r="K4" s="7" t="n"/>
       <c r="L4" s="7" t="n"/>
-      <c r="M4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -1084,7 +1058,6 @@
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
       <c r="L5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -1099,7 +1072,6 @@
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="7" t="n"/>
       <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -1114,7 +1086,6 @@
       <c r="J7" s="7" t="n"/>
       <c r="K7" s="7" t="n"/>
       <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -1129,7 +1100,6 @@
       <c r="J8" s="7" t="n"/>
       <c r="K8" s="7" t="n"/>
       <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -1144,7 +1114,6 @@
       <c r="J9" s="7" t="n"/>
       <c r="K9" s="7" t="n"/>
       <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -1159,7 +1128,6 @@
       <c r="J10" s="7" t="n"/>
       <c r="K10" s="7" t="n"/>
       <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -1174,7 +1142,6 @@
       <c r="J11" s="7" t="n"/>
       <c r="K11" s="7" t="n"/>
       <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -1189,7 +1156,6 @@
       <c r="J12" s="7" t="n"/>
       <c r="K12" s="7" t="n"/>
       <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -1204,7 +1170,6 @@
       <c r="J13" s="7" t="n"/>
       <c r="K13" s="7" t="n"/>
       <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
